--- a/manger/templates/题库导入测试.xlsx
+++ b/manger/templates/题库导入测试.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -429,7 +429,8 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,6 +501,11 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>编程语言</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>图片路径</t>
         </is>
       </c>
@@ -567,6 +573,7 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -631,6 +638,7 @@
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -699,6 +707,7 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -767,6 +776,7 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -823,6 +833,7 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -879,6 +890,7 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -927,6 +939,7 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -975,6 +988,7 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1023,6 +1037,7 @@
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1071,6 +1086,7 @@
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1127,6 +1143,7 @@
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1175,6 +1192,7 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1239,6 +1257,7 @@
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1303,6 +1322,7 @@
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1371,6 +1391,7 @@
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1427,6 +1448,7 @@
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1475,6 +1497,7 @@
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1523,6 +1546,7 @@
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1587,6 +1611,7 @@
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1651,6 +1676,7 @@
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1707,6 +1733,7 @@
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1755,6 +1782,216 @@
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PROGRAMMING</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>编写一个Java程序，计算两个整数的和并输出结果。程序需要从标准输入读取两个整数，计算它们的和，然后输出结果。
+要求：
+1. 使用Scanner类读取输入
+2. 计算两数之和
+3. 输出结果</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>import java.util.Scanner;
+public class Main {
+    public static void main(String[] args) {
+        Scanner scanner = new Scanner(System.in);
+        int a = scanner.nextInt();
+        int b = scanner.nextInt();
+        int sum = a + b;
+        System.out.println(sum);
+        scanner.close();
+    }
+}</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Java基础</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Java|输入输出|Scanner</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>使用Scanner类的nextInt()方法读取两个整数，然后计算它们的和并输出。</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>JAVA</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PROGRAMMING</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>编写一个Python程序，实现冒泡排序算法，对整数数组进行升序排序。
+要求：
+1. 方法签名：def bubble_sort(arr)
+2. 原地排序，修改原数组
+3. 使用冒泡排序算法
+4. 从标准输入读取整数（用空格分隔），排序后输出</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>def bubble_sort(arr):
+    n = len(arr)
+    for i in range(n):
+        for j in range(0, n - i - 1):
+            if arr[j] &gt; arr[j + 1]:
+                arr[j], arr[j + 1] = arr[j + 1], arr[j]
+if __name__ == "__main__":
+    arr = list(map(int, input().split()))
+    bubble_sort(arr)
+    print(" ".join(map(str, arr)))</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Python|排序|冒泡排序</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>冒泡排序通过多次遍历数组，比较相邻元素并交换位置，将较大的元素逐步"冒泡"到数组末尾。</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>PYTHON</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PROGRAMMING</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>编写一个C++程序，计算斐波那契数列的第n项。
+要求：
+1. 使用递归或循环实现
+2. 从标准输入读取一个整数n（n &gt;= 0）
+3. 输出斐波那契数列的第n项
+4. 斐波那契数列定义：F(0)=0, F(1)=1, F(n)=F(n-1)+F(n-2)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>#include &lt;iostream&gt;
+using namespace std;
+int fibonacci(int n) {
+    if (n &lt;= 1) return n;
+    int a = 0, b = 1, c;
+    for (int i = 2; i &lt;= n; i++) {
+        c = a + b;
+        a = b;
+        b = c;
+    }
+    return b;
+}
+int main() {
+    int n;
+    cin &gt;&gt; n;
+    cout &lt;&lt; fibonacci(n) &lt;&lt; endl;
+    return 0;
+}</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>C++|递归|斐波那契</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>斐波那契数列可以使用循环或递归实现。这里使用循环方式，时间复杂度为O(n)，空间复杂度为O(1)。</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>CPP</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/manger/templates/题库导入测试.xlsx
+++ b/manger/templates/题库导入测试.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -431,6 +431,7 @@
     <col width="30" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,6 +510,11 @@
           <t>图片路径</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>测试用例</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -574,6 +580,7 @@
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -639,6 +646,7 @@
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -708,6 +716,7 @@
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -777,6 +786,7 @@
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -834,6 +844,7 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -891,6 +902,7 @@
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -940,6 +952,7 @@
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -989,6 +1002,7 @@
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1038,6 +1052,7 @@
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1087,6 +1102,7 @@
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1144,6 +1160,7 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1193,6 +1210,7 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1258,6 +1276,7 @@
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1323,6 +1342,7 @@
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1392,6 +1412,7 @@
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1449,6 +1470,7 @@
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1498,6 +1520,7 @@
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1547,6 +1570,7 @@
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1612,6 +1636,7 @@
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1677,6 +1702,7 @@
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1734,6 +1760,7 @@
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1783,6 +1810,7 @@
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1850,6 +1878,14 @@
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>1
+2|3;5
+7|12;10
+20|30</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1917,6 +1953,11 @@
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>3 1 2|1 2 3;5 4 3 2 1|1 2 3 4 5</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1992,6 +2033,420 @@
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>0|0;1|1;5|5;10|55</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PROGRAMMING</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>输入n值，计算1到n之间(不包括n)所有偶数之和。</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>n = int(input())
+sum_even = 0
+for i in range(2, n, 2):
+    sum_even += i
+print(f"1到{n}之间所有的偶数和为{sum_even}")</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>EASY</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Python基础</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Python|循环|条件判断</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>使用range(2, n, 2)可以生成从2开始到n-1的所有偶数，然后累加求和。</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>PYTHON</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>11|1到11之间所有的偶数和为30;10|1到10之间所有的偶数和为20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PROGRAMMING</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>写一个函数，判断某个年份是否是闰年。从控制台接收用户输入的一个年份y(y&gt;1900)，调用函数，统计从1900年~y年(包括y)之间有多少个闰年。
+闰年判断规则：能被4整除但不能被100整除，或者能被400整除的年份是闰年。</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>def is_leap_year(year):
+    return (year % 4 == 0 and year % 100 != 0) or (year % 400 == 0)
+y = int(input())
+count = 0
+for year in range(1900, y + 1):
+    if is_leap_year(year):
+        count += 1
+print(f"从1900年到{y}年之间有{count}个闰年")</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Python基础</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Python|函数|循环|条件判断</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>闰年判断需要同时考虑能被4整除、不能被100整除，或者能被400整除的情况。</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>PYTHON</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2000|从1900年到2000年之间有25个闰年</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PROGRAMMING</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>写一个函数，判断某个年份是否是闰年。从控制台接收用户输入的一个年份y(y&lt;2080)，调用函数，统计从y到2100年(包括y和2100)之间有多少个闰年。
+闰年判断规则：能被4整除但不能被100整除，或者能被400整除的年份是闰年。</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>def is_leap_year(year):
+    return (year % 4 == 0 and year % 100 != 0) or (year % 400 == 0)
+y = int(input())
+count = 0
+for year in range(y, 2101):
+    if is_leap_year(year):
+        count += 1
+print(f"从{y}年到2100年之间有{count}个闰年")</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Python基础</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Python|函数|循环|条件判断</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>闰年判断需要同时考虑能被4整除、不能被100整除，或者能被400整除的情况。</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>PYTHON</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2023|从2023年到2100年之间有19个闰年</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PROGRAMMING</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>编写一个函数判定某个整数是否是素数。从控制台接收用户输入的两个正整数n1和n2，调用函数，统计n1~n2(包括n1和n2)之间有多少个素数，输出结果。
+素数指大于1且仅能被1和自己整除的整数。</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>def is_prime(num):
+    if num &lt; 2:
+        return False
+    for i in range(2, int(num ** 0.5) + 1):
+        if num % i == 0:
+            return False
+    return True
+n1 = int(input())
+n2 = int(input())
+count = 0
+for num in range(n1, n2 + 1):
+    if is_prime(num):
+        count += 1
+print(f"{n1}和{n2}之间有{count}个素数")</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Python|函数|素数|循环</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>判断素数时，只需要检查到sqrt(num)即可，因为如果num有大于sqrt(num)的因子，那么必然有小于sqrt(num)的因子。</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>PYTHON</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>9
+30|9和30之间有6个素数</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PROGRAMMING</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>定义一个判定某个整数是否是素数的函数。要求获取用户输入的正整数n，求n以内(不含n)所有素数之和并输出。
+素数指大于1且仅能被1和自己整除的整数。</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>def is_prime(num):
+    if num &lt; 2:
+        return False
+    for i in range(2, int(num ** 0.5) + 1):
+        if num % i == 0:
+            return False
+    return True
+n = int(input())
+sum_prime = 0
+for i in range(2, n):
+    if is_prime(i):
+        sum_prime += i
+print(f"{n}以内所有素数之和为{sum_prime}")</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Python|函数|素数|循环</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>判断素数时，只需要检查到sqrt(num)即可，因为如果num有大于sqrt(num)的因子，那么必然有小于sqrt(num)的因子。</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>PYTHON</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>7|7以内所有素数之和为10;2|2以内所有素数之和为0;3|3以内所有素数之和为2;10|10以内所有素数之和为17</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PROGRAMMING</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>先输入n值，然后输入n个整数，求这n个整数的和。</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>n = int(input())
+sum_val = 0
+for i in range(n):
+    num = int(input())
+    sum_val += num
+print(f"输入的{n}个整数和为{sum_val}")</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>EASY</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Python基础</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Python|循环|输入输出</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>使用循环读取n个整数并累加求和。</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>PYTHON</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>5
+1
+6
+7
+8
+9|输入的5个整数和为35;3
+2
+6
+7|输入的3个整数和为15</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
